--- a/artfynd/A 52723-2024 artfynd.xlsx
+++ b/artfynd/A 52723-2024 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>121338969</v>
       </c>
       <c r="B3" t="n">
-        <v>57501</v>
+        <v>57504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 52723-2024 artfynd.xlsx
+++ b/artfynd/A 52723-2024 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>121338969</v>
       </c>
       <c r="B3" t="n">
-        <v>57504</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 52723-2024 artfynd.xlsx
+++ b/artfynd/A 52723-2024 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>121338969</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>57508</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 52723-2024 artfynd.xlsx
+++ b/artfynd/A 52723-2024 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>121338969</v>
       </c>
       <c r="B3" t="n">
-        <v>57508</v>
+        <v>57509</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 52723-2024 artfynd.xlsx
+++ b/artfynd/A 52723-2024 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>121338969</v>
       </c>
       <c r="B3" t="n">
-        <v>57509</v>
+        <v>57510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
